--- a/hardware/rover_parts_list.xlsx
+++ b/hardware/rover_parts_list.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="59">
   <si>
     <t xml:space="preserve">Produkt</t>
   </si>
@@ -103,6 +103,9 @@
     <t xml:space="preserve">Header</t>
   </si>
   <si>
+    <t xml:space="preserve">verschiedene, siehe headers.xlsx</t>
+  </si>
+  <si>
     <t xml:space="preserve">Schalter</t>
   </si>
   <si>
@@ -188,6 +191,12 @@
   </si>
   <si>
     <t xml:space="preserve">USB-Kabel ½ A gelötet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ToF-Kabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christian nur 1/3 des Preises</t>
   </si>
 </sst>
 </file>
@@ -289,7 +298,7 @@
   <sheetFormatPr defaultColWidth="8.63671875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -320,21 +329,22 @@
         <v>7</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>5.07</v>
+        <f aca="false">5.07*1.19</f>
+        <v>6.0333</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="0" t="n">
         <f aca="false">B2*C2</f>
-        <v>5.07</v>
+        <v>6.0333</v>
       </c>
       <c r="E2" s="0" t="s">
         <v>8</v>
       </c>
       <c r="H2" s="0" t="n">
         <f aca="false">SUM(D2:D102)</f>
-        <v>25.1056</v>
+        <v>27.2239</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -564,22 +574,22 @@
         <v>26</v>
       </c>
       <c r="B16" s="0" t="n">
-        <v>1</v>
+        <v>2.16</v>
       </c>
       <c r="C16" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="0" t="n">
         <f aca="false">B16*C16</f>
-        <v>1</v>
+        <v>2.16</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" s="0" t="n">
         <v>0.48</v>
@@ -592,15 +602,15 @@
         <v>0.48</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>0.4</v>
@@ -610,12 +620,12 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" s="0" t="n">
         <v>0.65</v>
@@ -625,48 +635,42 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="0" t="n">
         <v>0.17</v>
       </c>
-      <c r="C20" s="0" t="n">
-        <v>1</v>
-      </c>
       <c r="D20" s="0" t="n">
         <f aca="false">B20*C20</f>
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B21" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="C21" s="0" t="n">
-        <v>1</v>
-      </c>
       <c r="D21" s="0" t="n">
         <f aca="false">B21*C21</f>
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B22" s="0" t="n">
         <v>0.2</v>
@@ -676,15 +680,15 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23" s="0" t="n">
         <v>0.07</v>
@@ -694,37 +698,37 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" s="0" t="n">
         <v>0.08</v>
       </c>
       <c r="C24" s="0" t="n">
         <f aca="false">4*C22+2*C20</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D24" s="0" t="n">
         <f aca="false">B24*C24</f>
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B25" s="0" t="n">
         <v>0.03</v>
@@ -737,12 +741,12 @@
         <v>0.03</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26" s="0" t="n">
         <v>5.95</v>
@@ -755,12 +759,12 @@
         <v>5.95</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B27" s="0" t="n">
         <v>0.51</v>
@@ -775,7 +779,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B28" s="0" t="n">
         <v>0.006</v>
@@ -788,12 +792,12 @@
         <v>0.012</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B29" s="0" t="n">
         <v>0.006</v>
@@ -811,7 +815,7 @@
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B30" s="0" t="n">
         <v>0.006</v>
@@ -824,12 +828,12 @@
         <v>0.012</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>0.005</v>
@@ -842,12 +846,12 @@
         <v>0.01</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B32" s="0" t="n">
         <v>0.006</v>
@@ -865,7 +869,7 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B33" s="0" t="n">
         <v>0.006</v>
@@ -883,7 +887,7 @@
     </row>
     <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B34" s="0" t="n">
         <v>0.065</v>
@@ -901,7 +905,7 @@
     </row>
     <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B35" s="0" t="n">
         <v>0.5</v>
@@ -916,7 +920,7 @@
     </row>
     <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B36" s="0" t="n">
         <v>0.12</v>
@@ -929,12 +933,12 @@
         <v>0.24</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B37" s="0" t="n">
         <v>0.081</v>
@@ -952,7 +956,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B38" s="0" t="n">
         <f aca="false">0.64/2</f>
@@ -966,7 +970,29 @@
         <v>0.32</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="0" t="n">
+        <f aca="false">3.75/10</f>
+        <v>0.375</v>
+      </c>
+      <c r="C39" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="0" t="n">
+        <f aca="false">B39*C39</f>
+        <v>0.375</v>
+      </c>
+      <c r="E39" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="F39" s="0" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -996,6 +1022,7 @@
     <hyperlink ref="E36" r:id="rId22" display="Pollin"/>
     <hyperlink ref="E37" r:id="rId23" display="Mouser"/>
     <hyperlink ref="E38" r:id="rId24" display="Pollin"/>
+    <hyperlink ref="E39" r:id="rId25" display="Pollin"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/hardware/rover_parts_list.xlsx
+++ b/hardware/rover_parts_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ruben\rover\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E6B28F-1420-42F6-A0CC-63948FD8D382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9416514-4620-4F4D-8502-1DD1D5A53C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,9 +110,6 @@
     <t>vorhanden</t>
   </si>
   <si>
-    <t>Pla</t>
-  </si>
-  <si>
     <t>Kabel</t>
   </si>
   <si>
@@ -213,6 +210,9 @@
   </si>
   <si>
     <t>Christian nur 1/3 des Preises</t>
+  </si>
+  <si>
+    <t>PLA</t>
   </si>
 </sst>
 </file>
@@ -634,7 +634,7 @@
       </c>
       <c r="H2">
         <f>SUM(D2:D102)</f>
-        <v>27.113900000000001</v>
+        <v>28.105900000000002</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -675,14 +675,14 @@
         <v>12</v>
       </c>
       <c r="B5">
-        <v>1.1000000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -782,12 +782,9 @@
       <c r="B11">
         <v>0.114</v>
       </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>0.22800000000000001</v>
+        <v>0</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -825,17 +822,17 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>2.04</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2.04</v>
       </c>
       <c r="E14" t="s">
         <v>23</v>
@@ -843,7 +840,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -861,7 +858,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>2.16</v>
@@ -874,12 +871,12 @@
         <v>2.16</v>
       </c>
       <c r="E16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>0.48</v>
@@ -892,15 +889,15 @@
         <v>0.48</v>
       </c>
       <c r="E17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" t="s">
         <v>29</v>
-      </c>
-      <c r="F17" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>0.4</v>
@@ -910,12 +907,12 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19">
         <v>0.65</v>
@@ -925,12 +922,12 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20">
         <v>0.17</v>
@@ -940,12 +937,12 @@
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21">
         <v>0.05</v>
@@ -955,12 +952,12 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22">
         <v>0.2</v>
@@ -970,15 +967,15 @@
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23">
         <v>7.0000000000000007E-2</v>
@@ -988,37 +985,33 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24">
         <v>0.08</v>
       </c>
-      <c r="C24">
-        <f>4*C22+2*C20</f>
+      <c r="D24">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D24">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="E24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25">
         <v>0.03</v>
@@ -1031,12 +1024,12 @@
         <v>0.03</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26">
         <v>5.95</v>
@@ -1049,27 +1042,27 @@
         <v>5.95</v>
       </c>
       <c r="E26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B27">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B28">
         <v>6.0000000000000001E-3</v>
@@ -1082,12 +1075,12 @@
         <v>1.2E-2</v>
       </c>
       <c r="E28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B29">
         <v>6.0000000000000001E-3</v>
@@ -1105,7 +1098,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B30">
         <v>6.0000000000000001E-3</v>
@@ -1118,12 +1111,12 @@
         <v>1.2E-2</v>
       </c>
       <c r="E30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B31">
         <v>5.0000000000000001E-3</v>
@@ -1136,12 +1129,12 @@
         <v>0.01</v>
       </c>
       <c r="E31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B32">
         <v>6.0000000000000001E-3</v>
@@ -1159,7 +1152,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B33">
         <v>6.0000000000000001E-3</v>
@@ -1177,7 +1170,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B34">
         <v>6.5000000000000002E-2</v>
@@ -1195,7 +1188,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B35">
         <v>0.5</v>
@@ -1210,7 +1203,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B36">
         <v>0.12</v>
@@ -1223,12 +1216,12 @@
         <v>0.24</v>
       </c>
       <c r="E36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B37">
         <v>8.1000000000000003E-2</v>
@@ -1246,7 +1239,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B38">
         <f>0.64/2</f>
@@ -1260,12 +1253,12 @@
         <v>0.32</v>
       </c>
       <c r="E38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B39">
         <f>3.75/10</f>
@@ -1279,10 +1272,10 @@
         <v>0.375</v>
       </c>
       <c r="E39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
